--- a/data/trans_orig/Q57-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q57-Edad-trans_orig.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la autopercepción de felicidad</t>
+          <t>Puntuación media de la autopercepción de felicidad (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -636,27 +636,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,73; 9,08</t>
+          <t>8,72; 9,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,08; 8,33</t>
+          <t>8,07; 8,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 8,78</t>
+          <t>8,33; 8,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 8,34</t>
+          <t>8,16; 8,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,63; 8,88</t>
+          <t>8,62; 8,9</t>
         </is>
       </c>
     </row>
@@ -711,22 +711,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 8,05</t>
+          <t>7,83; 8,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 8,58</t>
+          <t>8,18; 8,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,91; 8,12</t>
+          <t>7,9; 8,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,22; 8,53</t>
+          <t>8,19; 8,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,25; 8,5</t>
+          <t>8,25; 8,51</t>
         </is>
       </c>
     </row>
@@ -791,22 +791,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 7,98</t>
+          <t>7,76; 7,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 8,52</t>
+          <t>8,23; 8,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 7,95</t>
+          <t>7,74; 7,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,25; 8,47</t>
+          <t>8,27; 8,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -871,32 +871,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,59</t>
+          <t>7,32; 7,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 8,74</t>
+          <t>8,11; 8,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,52</t>
+          <t>7,26; 7,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 8,07</t>
+          <t>7,87; 8,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 7,52</t>
+          <t>7,33; 7,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,04; 8,55</t>
+          <t>8,03; 8,53</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,23</t>
+          <t>6,92; 7,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,63</t>
+          <t>7,39; 7,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,43</t>
+          <t>7,21; 7,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 7,7</t>
+          <t>7,5; 7,69</t>
         </is>
       </c>
     </row>
@@ -1031,32 +1031,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,18; 7,53</t>
+          <t>7,19; 7,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,74; 8,01</t>
+          <t>7,73; 8,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,67; 7,06</t>
+          <t>6,65; 7,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,57</t>
+          <t>7,12; 7,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,24</t>
+          <t>6,97; 7,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,28; 7,73</t>
+          <t>7,26; 7,72</t>
         </is>
       </c>
     </row>
@@ -1111,27 +1111,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,01</t>
+          <t>6,6; 7,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,62</t>
+          <t>7,28; 7,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,13; 6,58</t>
+          <t>6,1; 6,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,88; 7,17</t>
+          <t>6,86; 7,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,36; 6,69</t>
+          <t>6,38; 6,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,63; 7,74</t>
+          <t>7,64; 7,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,12; 8,38</t>
+          <t>8,13; 8,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,38; 7,5</t>
+          <t>7,39; 7,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,95; 8,13</t>
+          <t>7,94; 8,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q57-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q57-Edad-trans_orig.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>8,87</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,59</t>
+          <t>8,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,76</t>
+          <t>8,72</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 8,41</t>
+          <t>8,18; 8,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,72; 9,07</t>
+          <t>8,7; 9,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 8,77</t>
+          <t>8,31; 8,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,16; 8,33</t>
+          <t>8,17; 8,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,62; 8,9</t>
+          <t>8,57; 8,85</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,4</t>
+          <t>8,38</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,38</t>
+          <t>8,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,39</t>
+          <t>8,41</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,83; 8,05</t>
+          <t>7,81; 8,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,18; 8,55</t>
+          <t>8,19; 8,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 8,51</t>
+          <t>8,3; 8,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,9; 8,06</t>
+          <t>7,9; 8,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,25; 8,51</t>
+          <t>8,29; 8,52</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,39</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,37</t>
+          <t>8,35</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,38</t>
+          <t>8,35</t>
         </is>
       </c>
     </row>
@@ -791,22 +791,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,76; 7,99</t>
+          <t>7,75; 7,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 8,53</t>
+          <t>8,2; 8,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 7,94</t>
+          <t>7,73; 7,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,27; 8,47</t>
+          <t>8,26; 8,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,28; 8,47</t>
+          <t>8,26; 8,44</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,39</t>
+          <t>8,15</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,2</t>
+          <t>8,04</t>
         </is>
       </c>
     </row>
@@ -871,32 +871,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,61</t>
+          <t>7,3; 7,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 8,76</t>
+          <t>8,03; 8,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,53</t>
+          <t>7,26; 7,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 8,07</t>
+          <t>7,83; 8,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,52</t>
+          <t>7,33; 7,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 8,53</t>
+          <t>7,96; 8,11</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,69</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>7,5</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,69</t>
+          <t>7,42; 7,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 7,83</t>
+          <t>7,55; 7,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,26</t>
+          <t>6,91; 7,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,63</t>
+          <t>7,37; 7,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,42</t>
+          <t>7,2; 7,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,88</t>
+          <t>7,91</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,35</t>
+          <t>7,52</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,55</t>
+          <t>7,71</t>
         </is>
       </c>
     </row>
@@ -1031,32 +1031,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,52</t>
+          <t>7,19; 7,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,73; 8,01</t>
+          <t>7,78; 8,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,04</t>
+          <t>6,67; 7,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,57</t>
+          <t>7,38; 7,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,24</t>
+          <t>6,97; 7,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,72</t>
+          <t>7,61; 7,8</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,45</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1111,27 +1111,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,02</t>
+          <t>6,59; 7,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,28; 7,63</t>
+          <t>7,31; 7,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,1; 6,56</t>
+          <t>6,13; 6,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,17</t>
+          <t>6,88; 7,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,38; 6,71</t>
+          <t>6,37; 6,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8,21</t>
+          <t>8,14</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>7,9</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>8,02</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,64; 7,74</t>
+          <t>7,63; 7,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,13; 8,39</t>
+          <t>8,07; 8,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,7; 7,93</t>
+          <t>7,85; 7,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,52; 7,61</t>
+          <t>7,52; 7,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,94; 8,13</t>
+          <t>7,97; 8,05</t>
         </is>
       </c>
     </row>
